--- a/Supplementary Table S8.xlsx
+++ b/Supplementary Table S8.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JCC\OneDrive\Desktop\Proteome -Visualization &amp; Annotations\Top 5 proteins descriptors and annotations - fig3\Stacking all merged tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\Desktop\Proteome_analysis_S_AA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_178E6A8052D97BF7FFD092B4F15622C8E0E2942D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920C5F6F-47EF-4BA0-8E9B-65EE99120A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Compact_proteins" sheetId="1" r:id="rId1"/>
@@ -1317,8 +1317,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1346,8 +1354,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1651,158 +1668,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AW44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.5703125" customWidth="1"/>
+    <col min="4" max="4" width="42.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="9.140625" style="1"/>
+    <col min="15" max="15" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="22" width="9.140625" style="1"/>
+    <col min="23" max="25" width="9.140625" style="3"/>
+    <col min="26" max="26" width="9.140625" style="1"/>
+    <col min="27" max="27" width="9.140625" style="3"/>
+    <col min="28" max="28" width="9.140625" style="1"/>
+    <col min="29" max="29" width="9.140625" style="3"/>
+    <col min="30" max="30" width="9.28515625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="9.140625" style="1"/>
+    <col min="32" max="32" width="43" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="25.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="39.5703125" customWidth="1"/>
+    <col min="37" max="37" width="30.140625" customWidth="1"/>
+    <col min="38" max="38" width="26" customWidth="1"/>
+    <col min="39" max="39" width="25.42578125" customWidth="1"/>
+    <col min="40" max="40" width="33.85546875" customWidth="1"/>
+    <col min="41" max="41" width="36.85546875" style="1" customWidth="1"/>
+    <col min="42" max="42" width="29.85546875" customWidth="1"/>
+    <col min="43" max="43" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="19" customWidth="1"/>
+    <col min="45" max="45" width="17.85546875" customWidth="1"/>
+    <col min="46" max="46" width="15.28515625" customWidth="1"/>
+    <col min="47" max="47" width="57.5703125" customWidth="1"/>
+    <col min="48" max="48" width="18.85546875" customWidth="1"/>
+    <col min="49" max="49" width="23.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -1818,85 +1876,85 @@
       <c r="E2" t="s">
         <v>53</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>2</v>
       </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+      <c r="G2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1">
         <v>227</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>1.3215859030837001</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>22.466960352422909</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>23.78854625550661</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>-21.145374449339212</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>5.5555555555555554</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>3</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>38</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>38</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>-35</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>35</v>
       </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
+      <c r="V2" s="1">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3">
         <v>2.27</v>
       </c>
-      <c r="X2">
+      <c r="X2" s="3">
         <v>1.6913725490196081</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="3">
         <v>1.5974074074074069</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="Z2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA2">
+      <c r="AA2" s="3">
         <v>22.466960352422909</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="3">
         <v>11.8942731277533</v>
       </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
+      <c r="AD2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AG2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH2">
+      <c r="AH2" s="1">
         <v>1</v>
       </c>
       <c r="AI2" t="s">
@@ -1917,7 +1975,7 @@
       <c r="AN2" t="s">
         <v>63</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AO2" s="1" t="s">
         <v>64</v>
       </c>
       <c r="AP2" t="s">
@@ -1945,7 +2003,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -1961,85 +2019,85 @@
       <c r="E3" t="s">
         <v>53</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>2</v>
       </c>
-      <c r="G3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3">
+      <c r="G3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
         <v>2</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>2</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>234</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>1.2820512820512819</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>22.222222222222221</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>23.504273504273499</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>-20.94017094017094</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>5.4545454545454541</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>3</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>38</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>38</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>-35</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>35</v>
       </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
+      <c r="V3" s="1">
+        <v>0</v>
+      </c>
+      <c r="W3" s="3">
         <v>2.34</v>
       </c>
-      <c r="X3">
+      <c r="X3" s="3">
         <v>1.71</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" s="3">
         <v>1.616727272727273</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="Z3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA3">
+      <c r="AA3" s="3">
         <v>22.222222222222221</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="3">
         <v>12.39316239316239</v>
       </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="s">
+      <c r="AD3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AG3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH3">
+      <c r="AH3" s="1">
         <v>1</v>
       </c>
       <c r="AI3" t="s">
@@ -2060,7 +2118,7 @@
       <c r="AN3" t="s">
         <v>63</v>
       </c>
-      <c r="AO3" t="s">
+      <c r="AO3" s="1" t="s">
         <v>77</v>
       </c>
       <c r="AP3" t="s">
@@ -2088,7 +2146,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -2104,85 +2162,85 @@
       <c r="E4" t="s">
         <v>53</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>2</v>
       </c>
-      <c r="G4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4">
+      <c r="G4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
         <v>4</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>3</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>406</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>1.7241379310344831</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>10.3448275862069</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>12.068965517241381</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>-8.6206896551724146</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>14.285714285714279</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>4</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>34</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>36</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>-30</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>32</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="1">
         <v>2</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="3">
         <v>2.3199999999999998</v>
       </c>
-      <c r="X4">
+      <c r="X4" s="3">
         <v>3.2866666666666671</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" s="3">
         <v>2.9828571428571431</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="Z4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA4">
+      <c r="AA4" s="3">
         <v>10.3448275862069</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AB4" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="3">
         <v>8.8669950738916263</v>
       </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="s">
+      <c r="AD4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AG4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH4">
+      <c r="AH4" s="1">
         <v>1</v>
       </c>
       <c r="AI4" t="s">
@@ -2203,7 +2261,7 @@
       <c r="AN4" t="s">
         <v>87</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AO4" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AP4" t="s">
@@ -2231,7 +2289,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>49</v>
       </c>
@@ -2247,85 +2305,85 @@
       <c r="E5" t="s">
         <v>53</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>2</v>
       </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5">
+      <c r="G5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
         <v>5</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>4</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>407</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>1.7199017199017199</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>10.31941031941032</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>12.039312039312041</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>-8.5995085995085976</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>14.28571428571429</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>4</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>33</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>35</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>-29</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>31</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="1">
         <v>2</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="3">
         <v>2.3257142857142861</v>
       </c>
-      <c r="X5">
+      <c r="X5" s="3">
         <v>3.197857142857143</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" s="3">
         <v>2.907142857142857</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="Z5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA5">
+      <c r="AA5" s="3">
         <v>10.31941031941032</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AB5" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AC5">
+      <c r="AC5" s="3">
         <v>9.3366093366093352</v>
       </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="s">
+      <c r="AD5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG5" t="s">
+      <c r="AG5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH5">
+      <c r="AH5" s="1">
         <v>1</v>
       </c>
       <c r="AI5" t="s">
@@ -2346,7 +2404,7 @@
       <c r="AN5" t="s">
         <v>87</v>
       </c>
-      <c r="AO5" t="s">
+      <c r="AO5" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AP5" t="s">
@@ -2374,7 +2432,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -2390,82 +2448,82 @@
       <c r="E6" t="s">
         <v>97</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6">
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
         <v>5</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>216</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>2.3148148148148149</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>18.981481481481481</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>21.296296296296301</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>-16.666666666666661</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>10.869565217391299</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>5</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>32</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>34</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>-27</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>29</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="1">
         <v>2</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="3">
         <v>2.16</v>
       </c>
-      <c r="X6">
+      <c r="X6" s="3">
         <v>1.6858536585365851</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" s="3">
         <v>1.5965217391304349</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="Z6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA6">
+      <c r="AA6" s="3">
         <v>18.981481481481481</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AB6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC6">
+      <c r="AC6" s="3">
         <v>14.81481481481481</v>
       </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="s">
+      <c r="AD6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG6" t="s">
+      <c r="AG6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH6">
+      <c r="AH6" s="1">
         <v>1</v>
       </c>
       <c r="AI6" t="s">
@@ -2486,7 +2544,7 @@
       <c r="AN6" t="s">
         <v>100</v>
       </c>
-      <c r="AO6" t="s">
+      <c r="AO6" s="1" t="s">
         <v>101</v>
       </c>
       <c r="AP6" t="s">
@@ -2514,7 +2572,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -2530,82 +2588,82 @@
       <c r="E7" t="s">
         <v>106</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7">
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
         <v>3</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>214</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>0.93457943925233633</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>19.158878504672899</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>20.09345794392523</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>-18.22429906542056</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>4.6511627906976747</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>2</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>34</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>34</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>-32</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>32</v>
       </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
+      <c r="V7" s="1">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3">
         <v>2.14</v>
       </c>
-      <c r="X7">
+      <c r="X7" s="3">
         <v>1.7746341463414641</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="3">
         <v>1.692093023255814</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="Z7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA7">
+      <c r="AA7" s="3">
         <v>19.158878504672899</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AB7" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC7">
+      <c r="AC7" s="3">
         <v>14.01869158878505</v>
       </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="s">
+      <c r="AD7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG7" t="s">
+      <c r="AG7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH7">
+      <c r="AH7" s="1">
         <v>1</v>
       </c>
       <c r="AI7" t="s">
@@ -2626,7 +2684,7 @@
       <c r="AN7" t="s">
         <v>63</v>
       </c>
-      <c r="AO7" t="s">
+      <c r="AO7" s="1" t="s">
         <v>107</v>
       </c>
       <c r="AP7" t="s">
@@ -2654,7 +2712,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -2670,82 +2728,82 @@
       <c r="E8" t="s">
         <v>112</v>
       </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="K8">
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1">
         <v>322</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>10.559006211180121</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>2.1739130434782612</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>12.73291925465838</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>8.3850931677018643</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>82.926829268292693</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>28</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>7.0000000000000009</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>28</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>21</v>
       </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
+      <c r="U8" s="1">
+        <v>0</v>
+      </c>
+      <c r="V8" s="1">
         <v>21</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="3">
         <v>2.651764705882353</v>
       </c>
-      <c r="X8">
+      <c r="X8" s="3">
         <v>3.2200000000000011</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" s="3">
         <v>2.1990243902439031</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="Z8" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="AA8">
+      <c r="AA8" s="3">
         <v>10.559006211180121</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AB8" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AC8">
+      <c r="AC8" s="3">
         <v>8.695652173913043</v>
       </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="s">
+      <c r="AD8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG8" t="s">
+      <c r="AG8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH8">
+      <c r="AH8" s="1">
         <v>1</v>
       </c>
       <c r="AI8" t="s">
@@ -2766,7 +2824,7 @@
       <c r="AN8" t="s">
         <v>118</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="AO8" s="1" t="s">
         <v>119</v>
       </c>
       <c r="AP8" t="s">
@@ -2794,7 +2852,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -2810,82 +2868,82 @@
       <c r="E9" t="s">
         <v>112</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
         <v>2</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>182</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>15.934065934065931</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>0.5494505494505495</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>16.483516483516478</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>15.38461538461538</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>96.666666666666671</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>26</v>
       </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="S9">
+      <c r="R9" s="1">
+        <v>1</v>
+      </c>
+      <c r="S9" s="1">
         <v>27</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>25</v>
       </c>
-      <c r="U9">
-        <v>1</v>
-      </c>
-      <c r="V9">
+      <c r="U9" s="1">
+        <v>1</v>
+      </c>
+      <c r="V9" s="1">
         <v>26</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="3">
         <v>1.631724137931035</v>
       </c>
-      <c r="X9">
+      <c r="X9" s="3">
         <v>1.82</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" s="3">
         <v>1.6379999999999999</v>
       </c>
-      <c r="Z9" t="s">
+      <c r="Z9" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="AA9">
+      <c r="AA9" s="3">
         <v>15.934065934065931</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AB9" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="AC9">
+      <c r="AC9" s="3">
         <v>10.43956043956044</v>
       </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="s">
+      <c r="AD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG9" t="s">
+      <c r="AG9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH9">
+      <c r="AH9" s="1">
         <v>2</v>
       </c>
       <c r="AI9" t="s">
@@ -2906,7 +2964,7 @@
       <c r="AN9" t="s">
         <v>133</v>
       </c>
-      <c r="AO9" t="s">
+      <c r="AO9" s="1" t="s">
         <v>134</v>
       </c>
       <c r="AP9" t="s">
@@ -2934,7 +2992,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -2950,82 +3008,82 @@
       <c r="E10" t="s">
         <v>112</v>
       </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
         <v>3</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>396</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>7.3232323232323244</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>2.0202020202020199</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>9.3434343434343443</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>5.3030303030303028</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>78.378378378378372</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>24</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>5</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>25</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>19</v>
       </c>
-      <c r="U10">
-        <v>1</v>
-      </c>
-      <c r="V10">
+      <c r="U10" s="1">
+        <v>1</v>
+      </c>
+      <c r="V10" s="1">
         <v>20</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="3">
         <v>3.277241379310345</v>
       </c>
-      <c r="X10">
+      <c r="X10" s="3">
         <v>2.4750000000000001</v>
       </c>
-      <c r="Y10">
+      <c r="Y10" s="3">
         <v>2.675675675675675</v>
       </c>
-      <c r="Z10" t="s">
+      <c r="Z10" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AA10">
+      <c r="AA10" s="3">
         <v>10.606060606060611</v>
       </c>
-      <c r="AB10" t="s">
+      <c r="AB10" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC10">
+      <c r="AC10" s="3">
         <v>10.606060606060611</v>
       </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="s">
+      <c r="AD10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG10" t="s">
+      <c r="AG10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH10">
+      <c r="AH10" s="1">
         <v>2</v>
       </c>
       <c r="AI10" t="s">
@@ -3046,7 +3104,7 @@
       <c r="AN10" t="s">
         <v>133</v>
       </c>
-      <c r="AO10" t="s">
+      <c r="AO10" s="1" t="s">
         <v>141</v>
       </c>
       <c r="AP10" t="s">
@@ -3074,7 +3132,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -3090,82 +3148,82 @@
       <c r="E11" t="s">
         <v>112</v>
       </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11">
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
         <v>4</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>529</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>7.7504725897920608</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>0.75614366729678639</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>8.5066162570888473</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>6.9943289224952743</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>91.111111111111114</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>22</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>3</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>22</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>19</v>
       </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
+      <c r="U11" s="1">
+        <v>0</v>
+      </c>
+      <c r="V11" s="1">
         <v>19</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="3">
         <v>2.838536585365854</v>
       </c>
-      <c r="X11">
+      <c r="X11" s="3">
         <v>3.9674999999999998</v>
       </c>
-      <c r="Y11">
+      <c r="Y11" s="3">
         <v>2.5862222222222222</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="Z11" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AA11">
+      <c r="AA11" s="3">
         <v>15.879017013232509</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AB11" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AC11">
+      <c r="AC11" s="3">
         <v>15.879017013232509</v>
       </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="s">
+      <c r="AD11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG11" t="s">
+      <c r="AG11" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AH11">
+      <c r="AH11" s="1">
         <v>1</v>
       </c>
       <c r="AI11" t="s">
@@ -3186,7 +3244,7 @@
       <c r="AN11" t="s">
         <v>152</v>
       </c>
-      <c r="AO11" t="s">
+      <c r="AO11" s="1" t="s">
         <v>153</v>
       </c>
       <c r="AP11" t="s">
@@ -3214,7 +3272,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -3230,82 +3288,82 @@
       <c r="E12" t="s">
         <v>112</v>
       </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12">
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
         <v>5</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>559</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>6.9767441860465116</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>0.53667262969588547</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>7.5134168157423984</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>6.4400715563506257</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>92.857142857142847</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>22</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>2</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>22</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>20</v>
       </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
+      <c r="U12" s="1">
+        <v>0</v>
+      </c>
+      <c r="V12" s="1">
         <v>20</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="3">
         <v>3.1533333333333329</v>
       </c>
-      <c r="X12">
+      <c r="X12" s="3">
         <v>3.726666666666667</v>
       </c>
-      <c r="Y12">
+      <c r="Y12" s="3">
         <v>2.9280952380952381</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="Z12" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AA12">
+      <c r="AA12" s="3">
         <v>18.962432915921291</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AB12" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AC12">
+      <c r="AC12" s="3">
         <v>18.962432915921291</v>
       </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="s">
+      <c r="AD12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG12" t="s">
+      <c r="AG12" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AH12">
+      <c r="AH12" s="1">
         <v>1</v>
       </c>
       <c r="AI12" t="s">
@@ -3326,7 +3384,7 @@
       <c r="AN12" t="s">
         <v>152</v>
       </c>
-      <c r="AO12" t="s">
+      <c r="AO12" s="1" t="s">
         <v>153</v>
       </c>
       <c r="AP12" t="s">
@@ -3354,7 +3412,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>163</v>
       </c>
@@ -3370,85 +3428,85 @@
       <c r="E13" t="s">
         <v>53</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>2</v>
       </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13">
+      <c r="G13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1">
         <v>4</v>
       </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13">
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
         <v>309</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>2.2653721682847898</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>13.592233009708741</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>15.857605177993531</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>-11.326860841423951</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>14.28571428571429</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>5</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>34</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>36</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>-29</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>31</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="1">
         <v>2</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="3">
         <v>2.2071428571428569</v>
       </c>
-      <c r="X13">
+      <c r="X13" s="3">
         <v>2.5014285714285718</v>
       </c>
-      <c r="Y13">
+      <c r="Y13" s="3">
         <v>2.2702040816326532</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="Z13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA13">
+      <c r="AA13" s="3">
         <v>13.592233009708741</v>
       </c>
-      <c r="AB13" t="s">
+      <c r="AB13" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC13">
+      <c r="AC13" s="3">
         <v>9.3851132686084142</v>
       </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="s">
+      <c r="AD13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG13" t="s">
+      <c r="AG13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH13">
+      <c r="AH13" s="1">
         <v>1</v>
       </c>
       <c r="AI13" t="s">
@@ -3469,7 +3527,7 @@
       <c r="AN13" t="s">
         <v>169</v>
       </c>
-      <c r="AO13" t="s">
+      <c r="AO13" s="1" t="s">
         <v>170</v>
       </c>
       <c r="AP13" t="s">
@@ -3497,7 +3555,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>163</v>
       </c>
@@ -3513,85 +3571,85 @@
       <c r="E14" t="s">
         <v>53</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>2</v>
       </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14">
+      <c r="G14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1">
         <v>3</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>2</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>407</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>2.2113022113022112</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>10.565110565110571</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>12.77641277641278</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>-8.3538083538083541</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>17.30769230769231</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>5</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>34</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>36</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>-29</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>31</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="1">
         <v>2</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="3">
         <v>2.2611111111111111</v>
       </c>
-      <c r="X14">
+      <c r="X14" s="3">
         <v>3.2181395348837212</v>
       </c>
-      <c r="Y14">
+      <c r="Y14" s="3">
         <v>2.8176923076923082</v>
       </c>
-      <c r="Z14" t="s">
+      <c r="Z14" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA14">
+      <c r="AA14" s="3">
         <v>10.565110565110571</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="AB14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AC14">
+      <c r="AC14" s="3">
         <v>10.31941031941032</v>
       </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="s">
+      <c r="AD14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG14" t="s">
+      <c r="AG14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH14">
+      <c r="AH14" s="1">
         <v>1</v>
       </c>
       <c r="AI14" t="s">
@@ -3612,7 +3670,7 @@
       <c r="AN14" t="s">
         <v>169</v>
       </c>
-      <c r="AO14" t="s">
+      <c r="AO14" s="1" t="s">
         <v>177</v>
       </c>
       <c r="AP14" t="s">
@@ -3640,7 +3698,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>163</v>
       </c>
@@ -3656,85 +3714,85 @@
       <c r="E15" t="s">
         <v>53</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>2</v>
       </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15">
+      <c r="G15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1">
         <v>3</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>223</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>1.3452914798206279</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>21.076233183856498</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>22.421524663677129</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>-19.730941704035871</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>6.0000000000000009</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>3</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>35</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>35</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>-32</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>32</v>
       </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
+      <c r="V15" s="1">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
         <v>2.23</v>
       </c>
-      <c r="X15">
+      <c r="X15" s="3">
         <v>1.66063829787234</v>
       </c>
-      <c r="Y15">
+      <c r="Y15" s="3">
         <v>1.5609999999999999</v>
       </c>
-      <c r="Z15" t="s">
+      <c r="Z15" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA15">
+      <c r="AA15" s="3">
         <v>21.076233183856498</v>
       </c>
-      <c r="AB15" t="s">
+      <c r="AB15" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC15">
+      <c r="AC15" s="3">
         <v>15.24663677130045</v>
       </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="s">
+      <c r="AD15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG15" t="s">
+      <c r="AG15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH15">
+      <c r="AH15" s="1">
         <v>2</v>
       </c>
       <c r="AI15" t="s">
@@ -3755,7 +3813,7 @@
       <c r="AN15" t="s">
         <v>63</v>
       </c>
-      <c r="AO15" t="s">
+      <c r="AO15" s="1" t="s">
         <v>181</v>
       </c>
       <c r="AP15" t="s">
@@ -3783,7 +3841,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>163</v>
       </c>
@@ -3799,85 +3857,85 @@
       <c r="E16" t="s">
         <v>53</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>2</v>
       </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16">
+      <c r="G16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1">
         <v>2</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>4</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>206</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>2.912621359223301</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>18.932038834951459</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>21.844660194174761</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>-16.019417475728151</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>13.33333333333333</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>6</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>34</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>34</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>-28</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>28</v>
       </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
+      <c r="V16" s="1">
+        <v>0</v>
+      </c>
+      <c r="W16" s="3">
         <v>2.06</v>
       </c>
-      <c r="X16">
+      <c r="X16" s="3">
         <v>1.795897435897436</v>
       </c>
-      <c r="Y16">
+      <c r="Y16" s="3">
         <v>1.556444444444445</v>
       </c>
-      <c r="Z16" t="s">
+      <c r="Z16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA16">
+      <c r="AA16" s="3">
         <v>18.932038834951459</v>
       </c>
-      <c r="AB16" t="s">
+      <c r="AB16" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC16">
+      <c r="AC16" s="3">
         <v>13.106796116504849</v>
       </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="s">
+      <c r="AD16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG16" t="s">
+      <c r="AG16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH16">
+      <c r="AH16" s="1">
         <v>1</v>
       </c>
       <c r="AI16" t="s">
@@ -3898,7 +3956,7 @@
       <c r="AN16" t="s">
         <v>63</v>
       </c>
-      <c r="AO16" t="s">
+      <c r="AO16" s="1" t="s">
         <v>181</v>
       </c>
       <c r="AP16" t="s">
@@ -3926,7 +3984,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>163</v>
       </c>
@@ -3942,82 +4000,82 @@
       <c r="E17" t="s">
         <v>97</v>
       </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17">
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
         <v>5</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>877</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>2.2805017103762828</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>4.5610034207525656</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>6.8415051311288479</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>-2.2805017103762828</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>33.333333333333343</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>7.0000000000000009</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>21</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>26</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>-14</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>19</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="1">
         <v>5</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="3">
         <v>3.069500000000001</v>
       </c>
-      <c r="X17">
+      <c r="X17" s="3">
         <v>4.6042500000000004</v>
       </c>
-      <c r="Y17">
+      <c r="Y17" s="3">
         <v>3.800333333333334</v>
       </c>
-      <c r="Z17" t="s">
+      <c r="Z17" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AA17">
+      <c r="AA17" s="3">
         <v>13.22690992018244</v>
       </c>
-      <c r="AB17" t="s">
+      <c r="AB17" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AC17">
+      <c r="AC17" s="3">
         <v>13.22690992018244</v>
       </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="s">
+      <c r="AD17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG17" t="s">
+      <c r="AG17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH17">
+      <c r="AH17" s="1">
         <v>1</v>
       </c>
       <c r="AI17" t="s">
@@ -4038,7 +4096,7 @@
       <c r="AN17" t="s">
         <v>193</v>
       </c>
-      <c r="AO17" t="s">
+      <c r="AO17" s="1" t="s">
         <v>194</v>
       </c>
       <c r="AP17" t="s">
@@ -4066,7 +4124,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>163</v>
       </c>
@@ -4082,82 +4140,82 @@
       <c r="E18" t="s">
         <v>106</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18">
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
         <v>5</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>216</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>2.3148148148148149</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>13.425925925925929</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>15.74074074074074</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>-11.111111111111111</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>14.70588235294117</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>4</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>23</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>25</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>-19</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>21</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="1">
         <v>2</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="3">
         <v>1.728</v>
       </c>
-      <c r="X18">
+      <c r="X18" s="3">
         <v>1.713103448275862</v>
       </c>
-      <c r="Y18">
+      <c r="Y18" s="3">
         <v>1.588235294117647</v>
       </c>
-      <c r="Z18" t="s">
+      <c r="Z18" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA18">
+      <c r="AA18" s="3">
         <v>16.666666666666661</v>
       </c>
-      <c r="AB18" t="s">
+      <c r="AB18" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AC18">
+      <c r="AC18" s="3">
         <v>16.666666666666661</v>
       </c>
-      <c r="AD18">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="s">
+      <c r="AD18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG18" t="s">
+      <c r="AG18" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH18">
+      <c r="AH18" s="1">
         <v>1</v>
       </c>
       <c r="AI18" t="s">
@@ -4178,7 +4236,7 @@
       <c r="AN18" t="s">
         <v>152</v>
       </c>
-      <c r="AO18" t="s">
+      <c r="AO18" s="1" t="s">
         <v>204</v>
       </c>
       <c r="AP18" t="s">
@@ -4206,7 +4264,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>163</v>
       </c>
@@ -4222,82 +4280,82 @@
       <c r="E19" t="s">
         <v>112</v>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="K19">
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
         <v>487</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>8.0082135523613953</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>1.6427104722792609</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>9.6509240246406556</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>6.3655030800821342</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>82.978723404255319</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>24</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>3</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>25</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>21</v>
       </c>
-      <c r="U19">
-        <v>1</v>
-      </c>
-      <c r="V19">
+      <c r="U19" s="1">
+        <v>1</v>
+      </c>
+      <c r="V19" s="1">
         <v>22</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="3">
         <v>2.996923076923077</v>
       </c>
-      <c r="X19">
+      <c r="X19" s="3">
         <v>1.8262499999999999</v>
       </c>
-      <c r="Y19">
+      <c r="Y19" s="3">
         <v>2.5904255319148941</v>
       </c>
-      <c r="Z19" t="s">
+      <c r="Z19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AA19">
+      <c r="AA19" s="3">
         <v>9.4455852156057496</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="AB19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC19">
+      <c r="AC19" s="3">
         <v>9.4455852156057496</v>
       </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="s">
+      <c r="AD19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG19" t="s">
+      <c r="AG19" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH19">
+      <c r="AH19" s="1">
         <v>1</v>
       </c>
       <c r="AI19" t="s">
@@ -4318,7 +4376,7 @@
       <c r="AN19" t="s">
         <v>133</v>
       </c>
-      <c r="AO19" t="s">
+      <c r="AO19" s="1" t="s">
         <v>211</v>
       </c>
       <c r="AP19" t="s">
@@ -4346,7 +4404,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>163</v>
       </c>
@@ -4362,82 +4420,82 @@
       <c r="E20" t="s">
         <v>112</v>
       </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20">
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
         <v>2</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>960</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>3.75</v>
       </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
         <v>3.75</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>3.75</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>100</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>21</v>
       </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
+      <c r="R20" s="1">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1">
         <v>21</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>21</v>
       </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
+      <c r="U20" s="1">
+        <v>0</v>
+      </c>
+      <c r="V20" s="1">
         <v>21</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="3">
         <v>5.6</v>
       </c>
-      <c r="Y20">
+      <c r="Y20" s="3">
         <v>5.6</v>
       </c>
-      <c r="Z20" t="s">
+      <c r="Z20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AA20">
+      <c r="AA20" s="3">
         <v>13.125</v>
       </c>
-      <c r="AB20" t="s">
+      <c r="AB20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC20">
+      <c r="AC20" s="3">
         <v>13.125</v>
       </c>
-      <c r="AD20">
-        <v>1</v>
-      </c>
-      <c r="AE20" t="s">
+      <c r="AD20" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AF20" t="s">
+      <c r="AF20" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG20" t="s">
+      <c r="AG20" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AH20">
+      <c r="AH20" s="1">
         <v>2</v>
       </c>
       <c r="AI20" t="s">
@@ -4458,7 +4516,7 @@
       <c r="AN20" t="s">
         <v>220</v>
       </c>
-      <c r="AO20" t="s">
+      <c r="AO20" s="1" t="s">
         <v>221</v>
       </c>
       <c r="AP20" t="s">
@@ -4486,7 +4544,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>163</v>
       </c>
@@ -4502,82 +4560,82 @@
       <c r="E21" t="s">
         <v>112</v>
       </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21">
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
         <v>3</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>544</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>7.5367647058823524</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>0.73529411764705876</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>8.2720588235294112</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <v>6.8014705882352926</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="1">
         <v>91.111111111111114</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="1">
         <v>20</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="1">
         <v>3</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="1">
         <v>20</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="1">
         <v>17</v>
       </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
+      <c r="U21" s="1">
+        <v>0</v>
+      </c>
+      <c r="V21" s="1">
         <v>17</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="3">
         <v>2.653658536585366</v>
       </c>
-      <c r="X21">
+      <c r="X21" s="3">
         <v>4.08</v>
       </c>
-      <c r="Y21">
+      <c r="Y21" s="3">
         <v>2.4177777777777778</v>
       </c>
-      <c r="Z21" t="s">
+      <c r="Z21" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AA21">
+      <c r="AA21" s="3">
         <v>17.647058823529409</v>
       </c>
-      <c r="AB21" t="s">
+      <c r="AB21" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AC21">
+      <c r="AC21" s="3">
         <v>17.647058823529409</v>
       </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="s">
+      <c r="AD21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG21" t="s">
+      <c r="AG21" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AH21">
+      <c r="AH21" s="1">
         <v>1</v>
       </c>
       <c r="AI21" t="s">
@@ -4598,7 +4656,7 @@
       <c r="AN21" t="s">
         <v>152</v>
       </c>
-      <c r="AO21" t="s">
+      <c r="AO21" s="1" t="s">
         <v>153</v>
       </c>
       <c r="AP21" t="s">
@@ -4626,7 +4684,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>163</v>
       </c>
@@ -4642,82 +4700,82 @@
       <c r="E22" t="s">
         <v>112</v>
       </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22">
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
         <v>4</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>524</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="1">
         <v>6.2977099236641214</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="1">
         <v>0.76335877862595414</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="1">
         <v>7.0610687022900764</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="1">
         <v>5.5343511450381673</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="1">
         <v>89.189189189189193</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="1">
         <v>20</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="1">
         <v>2</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="1">
         <v>22</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="1">
         <v>18</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="1">
         <v>2</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="1">
         <v>20</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="3">
         <v>3.1757575757575758</v>
       </c>
-      <c r="X22">
+      <c r="X22" s="3">
         <v>2.62</v>
       </c>
-      <c r="Y22">
+      <c r="Y22" s="3">
         <v>3.1156756756756758</v>
       </c>
-      <c r="Z22" t="s">
+      <c r="Z22" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AA22">
+      <c r="AA22" s="3">
         <v>10.68702290076336</v>
       </c>
-      <c r="AB22" t="s">
+      <c r="AB22" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC22">
+      <c r="AC22" s="3">
         <v>10.68702290076336</v>
       </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="s">
+      <c r="AD22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="AG22" t="s">
+      <c r="AG22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH22" t="s">
+      <c r="AH22" s="1" t="s">
         <v>236</v>
       </c>
       <c r="AI22" t="s">
@@ -4738,7 +4796,7 @@
       <c r="AN22" t="s">
         <v>239</v>
       </c>
-      <c r="AO22" t="s">
+      <c r="AO22" s="1" t="s">
         <v>240</v>
       </c>
       <c r="AP22" t="s">
@@ -4766,7 +4824,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>163</v>
       </c>
@@ -4782,82 +4840,82 @@
       <c r="E23" t="s">
         <v>112</v>
       </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23">
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
         <v>5</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>669</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="1">
         <v>3.7369207772795221</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="1">
         <v>0.59790732436472349</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="1">
         <v>4.3348281016442449</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="1">
         <v>3.1390134529147979</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="1">
         <v>86.206896551724142</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="1">
         <v>18</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="1">
         <v>4</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="1">
         <v>18</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="1">
         <v>14</v>
       </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
+      <c r="U23" s="1">
+        <v>0</v>
+      </c>
+      <c r="V23" s="1">
         <v>14</v>
       </c>
-      <c r="W23">
+      <c r="W23" s="3">
         <v>4.8167999999999997</v>
       </c>
-      <c r="X23">
+      <c r="X23" s="3">
         <v>6.69</v>
       </c>
-      <c r="Y23">
+      <c r="Y23" s="3">
         <v>4.1524137931034488</v>
       </c>
-      <c r="Z23" t="s">
+      <c r="Z23" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AA23">
+      <c r="AA23" s="3">
         <v>19.133034379671152</v>
       </c>
-      <c r="AB23" t="s">
+      <c r="AB23" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AC23">
+      <c r="AC23" s="3">
         <v>19.133034379671152</v>
       </c>
-      <c r="AD23">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="s">
+      <c r="AD23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG23" t="s">
+      <c r="AG23" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AH23">
+      <c r="AH23" s="1">
         <v>1</v>
       </c>
       <c r="AI23" t="s">
@@ -4878,7 +4936,7 @@
       <c r="AN23" t="s">
         <v>250</v>
       </c>
-      <c r="AO23" t="s">
+      <c r="AO23" s="1" t="s">
         <v>251</v>
       </c>
       <c r="AP23" t="s">
@@ -4906,7 +4964,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>256</v>
       </c>
@@ -4922,85 +4980,85 @@
       <c r="E24" t="s">
         <v>97</v>
       </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24">
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1">
         <v>70</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="1">
         <v>17.142857142857139</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="1">
         <v>20</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="1">
         <v>37.142857142857139</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="1">
         <v>-2.8571428571428581</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="1">
         <v>46.153846153846153</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="1">
         <v>17.142857142857139</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="1">
         <v>20</v>
       </c>
-      <c r="S24">
+      <c r="S24" s="1">
         <v>37.142857142857153</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="1">
         <v>-2.8571428571428581</v>
       </c>
-      <c r="U24">
+      <c r="U24" s="1">
         <v>20</v>
       </c>
-      <c r="V24">
+      <c r="V24" s="1">
         <v>17.142857142857149</v>
       </c>
-      <c r="W24">
-        <v>1</v>
-      </c>
-      <c r="X24">
-        <v>1</v>
-      </c>
-      <c r="Y24">
-        <v>1</v>
-      </c>
-      <c r="Z24" t="s">
+      <c r="W24" s="3">
+        <v>1</v>
+      </c>
+      <c r="X24" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA24">
+      <c r="AA24" s="3">
         <v>20</v>
       </c>
-      <c r="AB24" t="s">
+      <c r="AB24" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="AC24">
+      <c r="AC24" s="3">
         <v>12.857142857142859</v>
       </c>
-      <c r="AD24">
+      <c r="AD24" s="1">
         <v>7</v>
       </c>
-      <c r="AE24" t="s">
+      <c r="AE24" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="AF24" t="s">
+      <c r="AF24" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG24" t="s">
+      <c r="AG24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH24">
+      <c r="AH24" s="1">
         <v>1</v>
       </c>
       <c r="AI24" t="s">
@@ -5021,7 +5079,7 @@
       <c r="AN24" t="s">
         <v>67</v>
       </c>
-      <c r="AO24" t="s">
+      <c r="AO24" s="1" t="s">
         <v>263</v>
       </c>
       <c r="AP24" t="s">
@@ -5049,7 +5107,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>256</v>
       </c>
@@ -5065,85 +5123,85 @@
       <c r="E25" t="s">
         <v>53</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>2</v>
       </c>
-      <c r="G25" t="b">
-        <v>1</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25">
+      <c r="G25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1">
         <v>2</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="1">
         <v>283</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="1">
         <v>1.7667844522968199</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="1">
         <v>17.667844522968199</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="1">
         <v>19.434628975265021</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="1">
         <v>-15.901060070671379</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="1">
         <v>9.0909090909090899</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="1">
         <v>4</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="1">
         <v>36</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="1">
         <v>36</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="1">
         <v>-32</v>
       </c>
-      <c r="U25">
+      <c r="U25" s="1">
         <v>32</v>
       </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
+      <c r="V25" s="1">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
         <v>2.2639999999999998</v>
       </c>
-      <c r="X25">
+      <c r="X25" s="3">
         <v>2.0375999999999999</v>
       </c>
-      <c r="Y25">
+      <c r="Y25" s="3">
         <v>1.852363636363636</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="Z25" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA25">
+      <c r="AA25" s="3">
         <v>17.667844522968199</v>
       </c>
-      <c r="AB25" t="s">
+      <c r="AB25" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC25">
+      <c r="AC25" s="3">
         <v>13.42756183745583</v>
       </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="s">
+      <c r="AD25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG25" t="s">
+      <c r="AG25" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH25">
+      <c r="AH25" s="1">
         <v>1</v>
       </c>
       <c r="AI25" t="s">
@@ -5164,7 +5222,7 @@
       <c r="AN25" t="s">
         <v>63</v>
       </c>
-      <c r="AO25" t="s">
+      <c r="AO25" s="1" t="s">
         <v>273</v>
       </c>
       <c r="AP25" t="s">
@@ -5192,7 +5250,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>256</v>
       </c>
@@ -5208,85 +5266,85 @@
       <c r="E26" t="s">
         <v>53</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <v>2</v>
       </c>
-      <c r="G26" t="b">
-        <v>1</v>
-      </c>
-      <c r="I26">
+      <c r="G26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1">
         <v>2</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="1">
         <v>3</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="1">
         <v>219</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="1">
         <v>2.2831050228310499</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="1">
         <v>20.091324200913238</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="1">
         <v>22.37442922374429</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="1">
         <v>-17.80821917808219</v>
       </c>
-      <c r="P26">
+      <c r="P26" s="1">
         <v>10.204081632653059</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="1">
         <v>5</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="1">
         <v>35</v>
       </c>
-      <c r="S26">
+      <c r="S26" s="1">
         <v>35</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="1">
         <v>-30</v>
       </c>
-      <c r="U26">
+      <c r="U26" s="1">
         <v>30</v>
       </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
+      <c r="V26" s="1">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>2.19</v>
       </c>
-      <c r="X26">
+      <c r="X26" s="3">
         <v>1.7420454545454549</v>
       </c>
-      <c r="Y26">
+      <c r="Y26" s="3">
         <v>1.5642857142857141</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="Z26" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA26">
+      <c r="AA26" s="3">
         <v>20.091324200913238</v>
       </c>
-      <c r="AB26" t="s">
+      <c r="AB26" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC26">
+      <c r="AC26" s="3">
         <v>11.415525114155249</v>
       </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="s">
+      <c r="AD26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG26" t="s">
+      <c r="AG26" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH26">
+      <c r="AH26" s="1">
         <v>1</v>
       </c>
       <c r="AI26" t="s">
@@ -5307,7 +5365,7 @@
       <c r="AN26" t="s">
         <v>63</v>
       </c>
-      <c r="AO26" t="s">
+      <c r="AO26" s="1" t="s">
         <v>279</v>
       </c>
       <c r="AP26" t="s">
@@ -5335,7 +5393,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>256</v>
       </c>
@@ -5351,85 +5409,85 @@
       <c r="E27" t="s">
         <v>53</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="1">
         <v>2</v>
       </c>
-      <c r="G27" t="b">
-        <v>1</v>
-      </c>
-      <c r="I27">
+      <c r="G27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1">
         <v>4</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="1">
         <v>4</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="1">
         <v>401</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="1">
         <v>1.745635910224439</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="1">
         <v>9.4763092269326688</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="1">
         <v>11.22194513715711</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="1">
         <v>-7.7306733167082298</v>
       </c>
-      <c r="P27">
+      <c r="P27" s="1">
         <v>15.555555555555561</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="1">
         <v>3</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="1">
         <v>31</v>
       </c>
-      <c r="S27">
+      <c r="S27" s="1">
         <v>34</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="1">
         <v>-28</v>
       </c>
-      <c r="U27">
+      <c r="U27" s="1">
         <v>31</v>
       </c>
-      <c r="V27">
+      <c r="V27" s="1">
         <v>3</v>
       </c>
-      <c r="W27">
+      <c r="W27" s="3">
         <v>1.7185714285714291</v>
       </c>
-      <c r="X27">
+      <c r="X27" s="3">
         <v>3.2713157894736842</v>
       </c>
-      <c r="Y27">
+      <c r="Y27" s="3">
         <v>3.0297777777777779</v>
       </c>
-      <c r="Z27" t="s">
+      <c r="Z27" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA27">
+      <c r="AA27" s="3">
         <v>9.4763092269326688</v>
       </c>
-      <c r="AB27" t="s">
+      <c r="AB27" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AC27">
+      <c r="AC27" s="3">
         <v>9.2269326683291766</v>
       </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="s">
+      <c r="AD27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG27" t="s">
+      <c r="AG27" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH27">
+      <c r="AH27" s="1">
         <v>1</v>
       </c>
       <c r="AI27" t="s">
@@ -5450,7 +5508,7 @@
       <c r="AN27" t="s">
         <v>87</v>
       </c>
-      <c r="AO27" t="s">
+      <c r="AO27" s="1" t="s">
         <v>263</v>
       </c>
       <c r="AP27" t="s">
@@ -5478,7 +5536,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>256</v>
       </c>
@@ -5494,85 +5552,85 @@
       <c r="E28" t="s">
         <v>53</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="1">
         <v>2</v>
       </c>
-      <c r="G28" t="b">
-        <v>1</v>
-      </c>
-      <c r="I28">
+      <c r="G28" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1">
         <v>3</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="1">
         <v>5</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="1">
         <v>399</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="1">
         <v>1.754385964912281</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="1">
         <v>9.5238095238095237</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="1">
         <v>11.278195488721799</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="1">
         <v>-7.7694235588972429</v>
       </c>
-      <c r="P28">
+      <c r="P28" s="1">
         <v>15.555555555555561</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" s="1">
         <v>3</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="1">
         <v>31</v>
       </c>
-      <c r="S28">
+      <c r="S28" s="1">
         <v>34</v>
       </c>
-      <c r="T28">
+      <c r="T28" s="1">
         <v>-28</v>
       </c>
-      <c r="U28">
+      <c r="U28" s="1">
         <v>31</v>
       </c>
-      <c r="V28">
+      <c r="V28" s="1">
         <v>3</v>
       </c>
-      <c r="W28">
+      <c r="W28" s="3">
         <v>1.71</v>
       </c>
-      <c r="X28">
+      <c r="X28" s="3">
         <v>3.2549999999999999</v>
       </c>
-      <c r="Y28">
+      <c r="Y28" s="3">
         <v>3.0146666666666668</v>
       </c>
-      <c r="Z28" t="s">
+      <c r="Z28" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AA28">
+      <c r="AA28" s="3">
         <v>9.7744360902255636</v>
       </c>
-      <c r="AB28" t="s">
+      <c r="AB28" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AC28">
+      <c r="AC28" s="3">
         <v>9.7744360902255636</v>
       </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="s">
+      <c r="AD28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG28" t="s">
+      <c r="AG28" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH28">
+      <c r="AH28" s="1">
         <v>1</v>
       </c>
       <c r="AI28" t="s">
@@ -5593,7 +5651,7 @@
       <c r="AN28" t="s">
         <v>292</v>
       </c>
-      <c r="AO28" t="s">
+      <c r="AO28" s="1" t="s">
         <v>293</v>
       </c>
       <c r="AP28" t="s">
@@ -5621,7 +5679,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>256</v>
       </c>
@@ -5637,82 +5695,82 @@
       <c r="E29" t="s">
         <v>106</v>
       </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29">
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1">
         <v>5</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="1">
         <v>186</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="1">
         <v>1.612903225806452</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="1">
         <v>17.20430107526882</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="1">
         <v>18.817204301075272</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="1">
         <v>-15.59139784946237</v>
       </c>
-      <c r="P29">
+      <c r="P29" s="1">
         <v>8.5714285714285694</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" s="1">
         <v>3</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="1">
         <v>29</v>
       </c>
-      <c r="S29">
+      <c r="S29" s="1">
         <v>30</v>
       </c>
-      <c r="T29">
+      <c r="T29" s="1">
         <v>-26</v>
       </c>
-      <c r="U29">
+      <c r="U29" s="1">
         <v>27</v>
       </c>
-      <c r="V29">
+      <c r="V29" s="1">
         <v>1.000000000000004</v>
       </c>
-      <c r="W29">
+      <c r="W29" s="3">
         <v>1.86</v>
       </c>
-      <c r="X29">
+      <c r="X29" s="3">
         <v>1.685624999999999</v>
       </c>
-      <c r="Y29">
+      <c r="Y29" s="3">
         <v>1.5942857142857141</v>
       </c>
-      <c r="Z29" t="s">
+      <c r="Z29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA29">
+      <c r="AA29" s="3">
         <v>17.20430107526882</v>
       </c>
-      <c r="AB29" t="s">
+      <c r="AB29" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AC29">
+      <c r="AC29" s="3">
         <v>8.064516129032258</v>
       </c>
-      <c r="AD29">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="s">
+      <c r="AD29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG29" t="s">
+      <c r="AG29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH29">
+      <c r="AH29" s="1">
         <v>1</v>
       </c>
       <c r="AI29" t="s">
@@ -5733,7 +5791,7 @@
       <c r="AN29" t="s">
         <v>300</v>
       </c>
-      <c r="AO29" t="s">
+      <c r="AO29" s="1" t="s">
         <v>263</v>
       </c>
       <c r="AP29" t="s">
@@ -5761,7 +5819,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>256</v>
       </c>
@@ -5777,82 +5835,82 @@
       <c r="E30" t="s">
         <v>112</v>
       </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="K30">
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30" s="1">
         <v>126</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="1">
         <v>24.603174603174601</v>
       </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
+      <c r="M30" s="1">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1">
         <v>24.603174603174601</v>
       </c>
-      <c r="O30">
+      <c r="O30" s="1">
         <v>24.603174603174601</v>
       </c>
-      <c r="P30">
+      <c r="P30" s="1">
         <v>100</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" s="1">
         <v>31</v>
       </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
+      <c r="R30" s="1">
+        <v>0</v>
+      </c>
+      <c r="S30" s="1">
         <v>31</v>
       </c>
-      <c r="T30">
+      <c r="T30" s="1">
         <v>31</v>
       </c>
-      <c r="U30">
-        <v>0</v>
-      </c>
-      <c r="V30">
+      <c r="U30" s="1">
+        <v>0</v>
+      </c>
+      <c r="V30" s="1">
         <v>31</v>
       </c>
-      <c r="W30">
+      <c r="W30" s="3">
         <v>1.26</v>
       </c>
-      <c r="Y30">
+      <c r="Y30" s="3">
         <v>1.26</v>
       </c>
-      <c r="Z30" t="s">
+      <c r="Z30" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AA30">
+      <c r="AA30" s="3">
         <v>32.539682539682538</v>
       </c>
-      <c r="AB30" t="s">
+      <c r="AB30" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AC30">
+      <c r="AC30" s="3">
         <v>32.539682539682538</v>
       </c>
-      <c r="AD30">
+      <c r="AD30" s="1">
         <v>9</v>
       </c>
-      <c r="AE30" t="s">
+      <c r="AE30" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="AF30" t="s">
+      <c r="AF30" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG30" t="s">
+      <c r="AG30" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH30">
+      <c r="AH30" s="1">
         <v>1</v>
       </c>
       <c r="AI30" t="s">
@@ -5873,7 +5931,7 @@
       <c r="AN30" t="s">
         <v>310</v>
       </c>
-      <c r="AO30" t="s">
+      <c r="AO30" s="1" t="s">
         <v>263</v>
       </c>
       <c r="AP30" t="s">
@@ -5901,7 +5959,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>256</v>
       </c>
@@ -5917,82 +5975,82 @@
       <c r="E31" t="s">
         <v>112</v>
       </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31">
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
         <v>2</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="1">
         <v>584</v>
       </c>
-      <c r="L31">
+      <c r="L31" s="1">
         <v>9.4178082191780828</v>
       </c>
-      <c r="M31">
+      <c r="M31" s="1">
         <v>0.68493150684931503</v>
       </c>
-      <c r="N31">
+      <c r="N31" s="1">
         <v>10.1027397260274</v>
       </c>
-      <c r="O31">
+      <c r="O31" s="1">
         <v>8.7328767123287676</v>
       </c>
-      <c r="P31">
+      <c r="P31" s="1">
         <v>93.220338983050837</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" s="1">
         <v>28</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="1">
         <v>3</v>
       </c>
-      <c r="S31">
+      <c r="S31" s="1">
         <v>28</v>
       </c>
-      <c r="T31">
+      <c r="T31" s="1">
         <v>25</v>
       </c>
-      <c r="U31">
-        <v>0</v>
-      </c>
-      <c r="V31">
+      <c r="U31" s="1">
+        <v>0</v>
+      </c>
+      <c r="V31" s="1">
         <v>25</v>
       </c>
-      <c r="W31">
+      <c r="W31" s="3">
         <v>2.9730909090909088</v>
       </c>
-      <c r="X31">
+      <c r="X31" s="3">
         <v>4.38</v>
       </c>
-      <c r="Y31">
+      <c r="Y31" s="3">
         <v>2.7715254237288138</v>
       </c>
-      <c r="Z31" t="s">
+      <c r="Z31" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AA31">
+      <c r="AA31" s="3">
         <v>17.465753424657539</v>
       </c>
-      <c r="AB31" t="s">
+      <c r="AB31" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AC31">
+      <c r="AC31" s="3">
         <v>17.465753424657539</v>
       </c>
-      <c r="AD31">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="s">
+      <c r="AD31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG31" t="s">
+      <c r="AG31" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AH31">
+      <c r="AH31" s="1">
         <v>1</v>
       </c>
       <c r="AI31" t="s">
@@ -6013,7 +6071,7 @@
       <c r="AN31" t="s">
         <v>152</v>
       </c>
-      <c r="AO31" t="s">
+      <c r="AO31" s="1" t="s">
         <v>263</v>
       </c>
       <c r="AP31" t="s">
@@ -6041,7 +6099,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="32" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>256</v>
       </c>
@@ -6057,82 +6115,82 @@
       <c r="E32" t="s">
         <v>112</v>
       </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32">
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
         <v>3</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="1">
         <v>1029</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="1">
         <v>3.6929057337220601</v>
       </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
+      <c r="M32" s="1">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1">
         <v>3.6929057337220601</v>
       </c>
-      <c r="O32">
+      <c r="O32" s="1">
         <v>3.6929057337220601</v>
       </c>
-      <c r="P32">
+      <c r="P32" s="1">
         <v>100</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="1">
         <v>25</v>
       </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
+      <c r="R32" s="1">
+        <v>0</v>
+      </c>
+      <c r="S32" s="1">
         <v>25</v>
       </c>
-      <c r="T32">
+      <c r="T32" s="1">
         <v>25</v>
       </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
+      <c r="U32" s="1">
+        <v>0</v>
+      </c>
+      <c r="V32" s="1">
         <v>25</v>
       </c>
-      <c r="W32">
+      <c r="W32" s="3">
         <v>6.7697368421052637</v>
       </c>
-      <c r="Y32">
+      <c r="Y32" s="3">
         <v>6.7697368421052637</v>
       </c>
-      <c r="Z32" t="s">
+      <c r="Z32" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AA32">
+      <c r="AA32" s="3">
         <v>14.18853255587949</v>
       </c>
-      <c r="AB32" t="s">
+      <c r="AB32" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC32">
+      <c r="AC32" s="3">
         <v>14.18853255587949</v>
       </c>
-      <c r="AD32">
-        <v>1</v>
-      </c>
-      <c r="AE32" t="s">
+      <c r="AD32" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE32" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AF32" t="s">
+      <c r="AF32" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG32" t="s">
+      <c r="AG32" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AH32">
+      <c r="AH32" s="1">
         <v>2</v>
       </c>
       <c r="AI32" t="s">
@@ -6153,7 +6211,7 @@
       <c r="AN32" t="s">
         <v>329</v>
       </c>
-      <c r="AO32" t="s">
+      <c r="AO32" s="1" t="s">
         <v>221</v>
       </c>
       <c r="AP32" t="s">
@@ -6181,7 +6239,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="33" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>256</v>
       </c>
@@ -6197,82 +6255,82 @@
       <c r="E33" t="s">
         <v>112</v>
       </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33">
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
         <v>4</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="1">
         <v>1021</v>
       </c>
-      <c r="L33">
+      <c r="L33" s="1">
         <v>3.2321253672869732</v>
       </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
+      <c r="M33" s="1">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1">
         <v>3.2321253672869732</v>
       </c>
-      <c r="O33">
+      <c r="O33" s="1">
         <v>3.2321253672869732</v>
       </c>
-      <c r="P33">
+      <c r="P33" s="1">
         <v>100</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" s="1">
         <v>25</v>
       </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
+      <c r="R33" s="1">
+        <v>0</v>
+      </c>
+      <c r="S33" s="1">
         <v>25</v>
       </c>
-      <c r="T33">
+      <c r="T33" s="1">
         <v>25</v>
       </c>
-      <c r="U33">
-        <v>0</v>
-      </c>
-      <c r="V33">
+      <c r="U33" s="1">
+        <v>0</v>
+      </c>
+      <c r="V33" s="1">
         <v>25</v>
       </c>
-      <c r="W33">
+      <c r="W33" s="3">
         <v>7.7348484848484853</v>
       </c>
-      <c r="Y33">
+      <c r="Y33" s="3">
         <v>7.7348484848484853</v>
       </c>
-      <c r="Z33" t="s">
+      <c r="Z33" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AA33">
+      <c r="AA33" s="3">
         <v>13.516160626836429</v>
       </c>
-      <c r="AB33" t="s">
+      <c r="AB33" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC33">
+      <c r="AC33" s="3">
         <v>13.516160626836429</v>
       </c>
-      <c r="AD33">
-        <v>1</v>
-      </c>
-      <c r="AE33" t="s">
+      <c r="AD33" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AF33" t="s">
+      <c r="AF33" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG33" t="s">
+      <c r="AG33" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AH33">
+      <c r="AH33" s="1">
         <v>2</v>
       </c>
       <c r="AI33" t="s">
@@ -6293,7 +6351,7 @@
       <c r="AN33" t="s">
         <v>329</v>
       </c>
-      <c r="AO33" t="s">
+      <c r="AO33" s="1" t="s">
         <v>263</v>
       </c>
       <c r="AP33" t="s">
@@ -6321,7 +6379,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>256</v>
       </c>
@@ -6337,82 +6395,82 @@
       <c r="E34" t="s">
         <v>112</v>
       </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34">
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
         <v>5</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="1">
         <v>323</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="1">
         <v>9.9071207430340564</v>
       </c>
-      <c r="M34">
+      <c r="M34" s="1">
         <v>1.5479876160990711</v>
       </c>
-      <c r="N34">
+      <c r="N34" s="1">
         <v>11.45510835913313</v>
       </c>
-      <c r="O34">
+      <c r="O34" s="1">
         <v>8.3591331269349851</v>
       </c>
-      <c r="P34">
+      <c r="P34" s="1">
         <v>86.486486486486484</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" s="1">
         <v>22</v>
       </c>
-      <c r="R34">
+      <c r="R34" s="1">
         <v>3</v>
       </c>
-      <c r="S34">
+      <c r="S34" s="1">
         <v>22</v>
       </c>
-      <c r="T34">
+      <c r="T34" s="1">
         <v>19</v>
       </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
+      <c r="U34" s="1">
+        <v>0</v>
+      </c>
+      <c r="V34" s="1">
         <v>19</v>
       </c>
-      <c r="W34">
+      <c r="W34" s="3">
         <v>2.2206250000000001</v>
       </c>
-      <c r="X34">
+      <c r="X34" s="3">
         <v>1.9379999999999999</v>
       </c>
-      <c r="Y34">
+      <c r="Y34" s="3">
         <v>1.92054054054054</v>
       </c>
-      <c r="Z34" t="s">
+      <c r="Z34" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AA34">
+      <c r="AA34" s="3">
         <v>11.14551083591331</v>
       </c>
-      <c r="AB34" t="s">
+      <c r="AB34" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC34">
+      <c r="AC34" s="3">
         <v>11.14551083591331</v>
       </c>
-      <c r="AD34">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="s">
+      <c r="AD34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG34" t="s">
+      <c r="AG34" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH34">
+      <c r="AH34" s="1">
         <v>1</v>
       </c>
       <c r="AI34" t="s">
@@ -6433,7 +6491,7 @@
       <c r="AN34" t="s">
         <v>133</v>
       </c>
-      <c r="AO34" t="s">
+      <c r="AO34" s="1" t="s">
         <v>343</v>
       </c>
       <c r="AP34" t="s">
@@ -6461,7 +6519,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="35" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>346</v>
       </c>
@@ -6477,85 +6535,85 @@
       <c r="E35" t="s">
         <v>53</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="1">
         <v>2</v>
       </c>
-      <c r="G35" t="b">
-        <v>1</v>
-      </c>
-      <c r="I35">
-        <v>1</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-      <c r="K35">
+      <c r="G35" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1">
+        <v>1</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1">
         <v>227</v>
       </c>
-      <c r="L35">
+      <c r="L35" s="1">
         <v>1.3215859030837001</v>
       </c>
-      <c r="M35">
+      <c r="M35" s="1">
         <v>21.58590308370044</v>
       </c>
-      <c r="N35">
+      <c r="N35" s="1">
         <v>22.907488986784141</v>
       </c>
-      <c r="O35">
+      <c r="O35" s="1">
         <v>-20.264317180616739</v>
       </c>
-      <c r="P35">
+      <c r="P35" s="1">
         <v>5.7692307692307692</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" s="1">
         <v>3</v>
       </c>
-      <c r="R35">
+      <c r="R35" s="1">
         <v>35</v>
       </c>
-      <c r="S35">
+      <c r="S35" s="1">
         <v>35</v>
       </c>
-      <c r="T35">
+      <c r="T35" s="1">
         <v>-32</v>
       </c>
-      <c r="U35">
+      <c r="U35" s="1">
         <v>32</v>
       </c>
-      <c r="V35">
-        <v>0</v>
-      </c>
-      <c r="W35">
+      <c r="V35" s="1">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>2.27</v>
       </c>
-      <c r="X35">
+      <c r="X35" s="3">
         <v>1.621428571428571</v>
       </c>
-      <c r="Y35">
+      <c r="Y35" s="3">
         <v>1.5278846153846151</v>
       </c>
-      <c r="Z35" t="s">
+      <c r="Z35" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA35">
+      <c r="AA35" s="3">
         <v>21.58590308370044</v>
       </c>
-      <c r="AB35" t="s">
+      <c r="AB35" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC35">
+      <c r="AC35" s="3">
         <v>12.77533039647577</v>
       </c>
-      <c r="AD35">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="s">
+      <c r="AD35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG35" t="s">
+      <c r="AG35" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH35">
+      <c r="AH35" s="1">
         <v>1</v>
       </c>
       <c r="AI35" t="s">
@@ -6576,7 +6634,7 @@
       <c r="AN35" t="s">
         <v>63</v>
       </c>
-      <c r="AO35" t="s">
+      <c r="AO35" s="1" t="s">
         <v>181</v>
       </c>
       <c r="AP35" t="s">
@@ -6604,7 +6662,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>346</v>
       </c>
@@ -6620,85 +6678,85 @@
       <c r="E36" t="s">
         <v>53</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="1">
         <v>2</v>
       </c>
-      <c r="G36" t="b">
-        <v>1</v>
-      </c>
-      <c r="I36">
+      <c r="G36" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1">
         <v>2</v>
       </c>
-      <c r="J36">
+      <c r="J36" s="1">
         <v>2</v>
       </c>
-      <c r="K36">
+      <c r="K36" s="1">
         <v>400</v>
       </c>
-      <c r="L36">
+      <c r="L36" s="1">
         <v>1.75</v>
       </c>
-      <c r="M36">
+      <c r="M36" s="1">
         <v>9.5</v>
       </c>
-      <c r="N36">
+      <c r="N36" s="1">
         <v>11.25</v>
       </c>
-      <c r="O36">
+      <c r="O36" s="1">
         <v>-7.75</v>
       </c>
-      <c r="P36">
+      <c r="P36" s="1">
         <v>15.555555555555561</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" s="1">
         <v>5</v>
       </c>
-      <c r="R36">
+      <c r="R36" s="1">
         <v>31</v>
       </c>
-      <c r="S36">
+      <c r="S36" s="1">
         <v>33</v>
       </c>
-      <c r="T36">
+      <c r="T36" s="1">
         <v>-26</v>
       </c>
-      <c r="U36">
+      <c r="U36" s="1">
         <v>28</v>
       </c>
-      <c r="V36">
+      <c r="V36" s="1">
         <v>2</v>
       </c>
-      <c r="W36">
+      <c r="W36" s="3">
         <v>2.8571428571428572</v>
       </c>
-      <c r="X36">
+      <c r="X36" s="3">
         <v>3.263157894736842</v>
       </c>
-      <c r="Y36">
+      <c r="Y36" s="3">
         <v>2.9333333333333331</v>
       </c>
-      <c r="Z36" t="s">
+      <c r="Z36" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA36">
+      <c r="AA36" s="3">
         <v>9.5</v>
       </c>
-      <c r="AB36" t="s">
+      <c r="AB36" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AC36">
+      <c r="AC36" s="3">
         <v>9.25</v>
       </c>
-      <c r="AD36">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="s">
+      <c r="AD36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG36" t="s">
+      <c r="AG36" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH36">
+      <c r="AH36" s="1">
         <v>1</v>
       </c>
       <c r="AI36" t="s">
@@ -6719,7 +6777,7 @@
       <c r="AN36" t="s">
         <v>87</v>
       </c>
-      <c r="AO36" t="s">
+      <c r="AO36" s="1" t="s">
         <v>263</v>
       </c>
       <c r="AP36" t="s">
@@ -6747,7 +6805,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>346</v>
       </c>
@@ -6763,88 +6821,88 @@
       <c r="E37" t="s">
         <v>360</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="1">
         <v>2</v>
       </c>
-      <c r="G37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37">
+      <c r="G37" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" s="1">
         <v>5</v>
       </c>
-      <c r="J37">
+      <c r="J37" s="1">
         <v>3</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="1">
         <v>110</v>
       </c>
-      <c r="L37">
+      <c r="L37" s="1">
         <v>18.18181818181818</v>
       </c>
-      <c r="M37">
+      <c r="M37" s="1">
         <v>5.4545454545454541</v>
       </c>
-      <c r="N37">
+      <c r="N37" s="1">
         <v>23.63636363636364</v>
       </c>
-      <c r="O37">
+      <c r="O37" s="1">
         <v>12.72727272727273</v>
       </c>
-      <c r="P37">
+      <c r="P37" s="1">
         <v>76.923076923076934</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" s="1">
         <v>20</v>
       </c>
-      <c r="R37">
+      <c r="R37" s="1">
         <v>6</v>
       </c>
-      <c r="S37">
+      <c r="S37" s="1">
         <v>26</v>
       </c>
-      <c r="T37">
+      <c r="T37" s="1">
         <v>14</v>
       </c>
-      <c r="U37">
+      <c r="U37" s="1">
         <v>6</v>
       </c>
-      <c r="V37">
+      <c r="V37" s="1">
         <v>20</v>
       </c>
-      <c r="W37">
+      <c r="W37" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="X37">
+      <c r="X37" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Y37">
+      <c r="Y37" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Z37" t="s">
+      <c r="Z37" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="AA37">
+      <c r="AA37" s="3">
         <v>18.18181818181818</v>
       </c>
-      <c r="AB37" t="s">
+      <c r="AB37" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="AC37">
+      <c r="AC37" s="3">
         <v>15.45454545454545</v>
       </c>
-      <c r="AD37">
+      <c r="AD37" s="1">
         <v>4</v>
       </c>
-      <c r="AE37" t="s">
+      <c r="AE37" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="AF37" t="s">
+      <c r="AF37" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG37" t="s">
+      <c r="AG37" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH37">
+      <c r="AH37" s="1">
         <v>1</v>
       </c>
       <c r="AI37" t="s">
@@ -6865,7 +6923,7 @@
       <c r="AN37" t="s">
         <v>366</v>
       </c>
-      <c r="AO37" t="s">
+      <c r="AO37" s="1" t="s">
         <v>367</v>
       </c>
       <c r="AP37" t="s">
@@ -6893,7 +6951,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>346</v>
       </c>
@@ -6909,85 +6967,85 @@
       <c r="E38" t="s">
         <v>53</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="1">
         <v>2</v>
       </c>
-      <c r="G38" t="b">
-        <v>1</v>
-      </c>
-      <c r="I38">
+      <c r="G38" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1">
         <v>3</v>
       </c>
-      <c r="J38">
+      <c r="J38" s="1">
         <v>4</v>
       </c>
-      <c r="K38">
+      <c r="K38" s="1">
         <v>54</v>
       </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
         <v>25.92592592592592</v>
       </c>
-      <c r="N38">
+      <c r="N38" s="1">
         <v>25.92592592592592</v>
       </c>
-      <c r="O38">
+      <c r="O38" s="1">
         <v>-25.92592592592592</v>
       </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
-      <c r="R38">
+      <c r="P38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>0</v>
+      </c>
+      <c r="R38" s="1">
         <v>25.92592592592592</v>
       </c>
-      <c r="S38">
+      <c r="S38" s="1">
         <v>25.92592592592592</v>
       </c>
-      <c r="T38">
+      <c r="T38" s="1">
         <v>-25.92592592592592</v>
       </c>
-      <c r="U38">
+      <c r="U38" s="1">
         <v>25.92592592592592</v>
       </c>
-      <c r="V38">
-        <v>0</v>
-      </c>
-      <c r="X38">
-        <v>1</v>
-      </c>
-      <c r="Y38">
-        <v>1</v>
-      </c>
-      <c r="Z38" t="s">
+      <c r="V38" s="1">
+        <v>0</v>
+      </c>
+      <c r="X38" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y38" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA38">
+      <c r="AA38" s="3">
         <v>25.92592592592592</v>
       </c>
-      <c r="AB38" t="s">
+      <c r="AB38" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="AC38">
+      <c r="AC38" s="3">
         <v>9.2592592592592595</v>
       </c>
-      <c r="AD38">
+      <c r="AD38" s="1">
         <v>3</v>
       </c>
-      <c r="AE38" t="s">
+      <c r="AE38" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="AF38" t="s">
+      <c r="AF38" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG38" t="s">
+      <c r="AG38" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AH38">
+      <c r="AH38" s="1">
         <v>1</v>
       </c>
       <c r="AI38" t="s">
@@ -7008,7 +7066,7 @@
       <c r="AN38" t="s">
         <v>379</v>
       </c>
-      <c r="AO38" t="s">
+      <c r="AO38" s="1" t="s">
         <v>380</v>
       </c>
       <c r="AP38" t="s">
@@ -7036,7 +7094,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>346</v>
       </c>
@@ -7052,85 +7110,85 @@
       <c r="E39" t="s">
         <v>53</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="1">
         <v>2</v>
       </c>
-      <c r="G39" t="b">
-        <v>1</v>
-      </c>
-      <c r="I39">
+      <c r="G39" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" s="1">
         <v>4</v>
       </c>
-      <c r="J39">
+      <c r="J39" s="1">
         <v>5</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="1">
         <v>8</v>
       </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
         <v>25</v>
       </c>
-      <c r="N39">
+      <c r="N39" s="1">
         <v>25</v>
       </c>
-      <c r="O39">
+      <c r="O39" s="1">
         <v>-25</v>
       </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
-        <v>0</v>
-      </c>
-      <c r="R39">
+      <c r="P39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>0</v>
+      </c>
+      <c r="R39" s="1">
         <v>25</v>
       </c>
-      <c r="S39">
+      <c r="S39" s="1">
         <v>25</v>
       </c>
-      <c r="T39">
+      <c r="T39" s="1">
         <v>-25</v>
       </c>
-      <c r="U39">
+      <c r="U39" s="1">
         <v>25</v>
       </c>
-      <c r="V39">
-        <v>0</v>
-      </c>
-      <c r="X39">
-        <v>1</v>
-      </c>
-      <c r="Y39">
-        <v>1</v>
-      </c>
-      <c r="Z39" t="s">
+      <c r="V39" s="1">
+        <v>0</v>
+      </c>
+      <c r="X39" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y39" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA39">
+      <c r="AA39" s="3">
         <v>25</v>
       </c>
-      <c r="AB39" t="s">
+      <c r="AB39" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="AC39">
+      <c r="AC39" s="3">
         <v>12.5</v>
       </c>
-      <c r="AD39">
+      <c r="AD39" s="1">
         <v>13</v>
       </c>
-      <c r="AE39" t="s">
+      <c r="AE39" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="AF39" t="s">
+      <c r="AF39" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG39" t="s">
+      <c r="AG39" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH39">
+      <c r="AH39" s="1">
         <v>1</v>
       </c>
       <c r="AI39" t="s">
@@ -7151,7 +7209,7 @@
       <c r="AN39" t="s">
         <v>67</v>
       </c>
-      <c r="AO39" t="s">
+      <c r="AO39" s="1" t="s">
         <v>263</v>
       </c>
       <c r="AP39" t="s">
@@ -7179,7 +7237,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>346</v>
       </c>
@@ -7195,82 +7253,82 @@
       <c r="E40" t="s">
         <v>106</v>
       </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-      <c r="G40" t="b">
-        <v>0</v>
-      </c>
-      <c r="I40">
+      <c r="F40" s="1">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" s="1">
         <v>5</v>
       </c>
-      <c r="K40">
+      <c r="K40" s="1">
         <v>54</v>
       </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1">
         <v>24.074074074074069</v>
       </c>
-      <c r="N40">
+      <c r="N40" s="1">
         <v>24.074074074074069</v>
       </c>
-      <c r="O40">
+      <c r="O40" s="1">
         <v>-24.074074074074069</v>
       </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>0</v>
-      </c>
-      <c r="R40">
+      <c r="P40" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>0</v>
+      </c>
+      <c r="R40" s="1">
         <v>24.074074074074069</v>
       </c>
-      <c r="S40">
+      <c r="S40" s="1">
         <v>24.074074074074069</v>
       </c>
-      <c r="T40">
+      <c r="T40" s="1">
         <v>-24.074074074074069</v>
       </c>
-      <c r="U40">
+      <c r="U40" s="1">
         <v>24.074074074074069</v>
       </c>
-      <c r="V40">
-        <v>0</v>
-      </c>
-      <c r="X40">
-        <v>1</v>
-      </c>
-      <c r="Y40">
-        <v>1</v>
-      </c>
-      <c r="Z40" t="s">
+      <c r="V40" s="1">
+        <v>0</v>
+      </c>
+      <c r="X40" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y40" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA40">
+      <c r="AA40" s="3">
         <v>24.074074074074069</v>
       </c>
-      <c r="AB40" t="s">
+      <c r="AB40" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="AC40">
+      <c r="AC40" s="3">
         <v>7.4074074074074074</v>
       </c>
-      <c r="AD40">
+      <c r="AD40" s="1">
         <v>4</v>
       </c>
-      <c r="AE40" t="s">
+      <c r="AE40" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="AF40" t="s">
+      <c r="AF40" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG40" t="s">
+      <c r="AG40" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH40">
+      <c r="AH40" s="1">
         <v>1</v>
       </c>
       <c r="AI40" t="s">
@@ -7291,7 +7349,7 @@
       <c r="AN40" t="s">
         <v>399</v>
       </c>
-      <c r="AO40" t="s">
+      <c r="AO40" s="1" t="s">
         <v>263</v>
       </c>
       <c r="AP40" t="s">
@@ -7319,7 +7377,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>346</v>
       </c>
@@ -7335,82 +7393,82 @@
       <c r="E41" t="s">
         <v>112</v>
       </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-      <c r="K41">
+      <c r="F41" s="1">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="K41" s="1">
         <v>995</v>
       </c>
-      <c r="L41">
+      <c r="L41" s="1">
         <v>3.316582914572864</v>
       </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1">
         <v>3.316582914572864</v>
       </c>
-      <c r="O41">
+      <c r="O41" s="1">
         <v>3.316582914572864</v>
       </c>
-      <c r="P41">
+      <c r="P41" s="1">
         <v>100</v>
       </c>
-      <c r="Q41">
+      <c r="Q41" s="1">
         <v>22</v>
       </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
+      <c r="R41" s="1">
+        <v>0</v>
+      </c>
+      <c r="S41" s="1">
         <v>22</v>
       </c>
-      <c r="T41">
+      <c r="T41" s="1">
         <v>22</v>
       </c>
-      <c r="U41">
-        <v>0</v>
-      </c>
-      <c r="V41">
+      <c r="U41" s="1">
+        <v>0</v>
+      </c>
+      <c r="V41" s="1">
         <v>22</v>
       </c>
-      <c r="W41">
+      <c r="W41" s="3">
         <v>6.6333333333333329</v>
       </c>
-      <c r="Y41">
+      <c r="Y41" s="3">
         <v>6.6333333333333329</v>
       </c>
-      <c r="Z41" t="s">
+      <c r="Z41" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AA41">
+      <c r="AA41" s="3">
         <v>13.06532663316583</v>
       </c>
-      <c r="AB41" t="s">
+      <c r="AB41" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC41">
+      <c r="AC41" s="3">
         <v>13.06532663316583</v>
       </c>
-      <c r="AD41">
-        <v>1</v>
-      </c>
-      <c r="AE41" t="s">
+      <c r="AD41" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE41" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AF41" t="s">
+      <c r="AF41" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG41" t="s">
+      <c r="AG41" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AH41">
+      <c r="AH41" s="1">
         <v>2</v>
       </c>
       <c r="AI41" t="s">
@@ -7431,7 +7489,7 @@
       <c r="AN41" t="s">
         <v>329</v>
       </c>
-      <c r="AO41" t="s">
+      <c r="AO41" s="1" t="s">
         <v>221</v>
       </c>
       <c r="AP41" t="s">
@@ -7459,7 +7517,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>346</v>
       </c>
@@ -7475,82 +7533,82 @@
       <c r="E42" t="s">
         <v>112</v>
       </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="G42" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42">
+      <c r="F42" s="1">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
         <v>2</v>
       </c>
-      <c r="K42">
+      <c r="K42" s="1">
         <v>477</v>
       </c>
-      <c r="L42">
+      <c r="L42" s="1">
         <v>6.9182389937106921</v>
       </c>
-      <c r="M42">
+      <c r="M42" s="1">
         <v>1.8867924528301889</v>
       </c>
-      <c r="N42">
+      <c r="N42" s="1">
         <v>8.8050314465408803</v>
       </c>
-      <c r="O42">
+      <c r="O42" s="1">
         <v>5.0314465408805038</v>
       </c>
-      <c r="P42">
+      <c r="P42" s="1">
         <v>78.571428571428584</v>
       </c>
-      <c r="Q42">
+      <c r="Q42" s="1">
         <v>21</v>
       </c>
-      <c r="R42">
+      <c r="R42" s="1">
         <v>7.0000000000000009</v>
       </c>
-      <c r="S42">
+      <c r="S42" s="1">
         <v>21</v>
       </c>
-      <c r="T42">
+      <c r="T42" s="1">
         <v>14</v>
       </c>
-      <c r="U42">
-        <v>0</v>
-      </c>
-      <c r="V42">
+      <c r="U42" s="1">
+        <v>0</v>
+      </c>
+      <c r="V42" s="1">
         <v>14</v>
       </c>
-      <c r="W42">
+      <c r="W42" s="3">
         <v>3.0354545454545452</v>
       </c>
-      <c r="X42">
+      <c r="X42" s="3">
         <v>3.71</v>
       </c>
-      <c r="Y42">
+      <c r="Y42" s="3">
         <v>2.3849999999999998</v>
       </c>
-      <c r="Z42" t="s">
+      <c r="Z42" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AA42">
+      <c r="AA42" s="3">
         <v>12.57861635220126</v>
       </c>
-      <c r="AB42" t="s">
+      <c r="AB42" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC42">
+      <c r="AC42" s="3">
         <v>12.57861635220126</v>
       </c>
-      <c r="AD42">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="s">
+      <c r="AD42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG42" t="s">
+      <c r="AG42" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH42">
+      <c r="AH42" s="1">
         <v>2</v>
       </c>
       <c r="AI42" t="s">
@@ -7571,7 +7629,7 @@
       <c r="AN42" t="s">
         <v>133</v>
       </c>
-      <c r="AO42" t="s">
+      <c r="AO42" s="1" t="s">
         <v>409</v>
       </c>
       <c r="AP42" t="s">
@@ -7599,7 +7657,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="43" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>346</v>
       </c>
@@ -7615,82 +7673,82 @@
       <c r="E43" t="s">
         <v>112</v>
       </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43">
+      <c r="F43" s="1">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
         <v>3</v>
       </c>
-      <c r="K43">
+      <c r="K43" s="1">
         <v>395</v>
       </c>
-      <c r="L43">
+      <c r="L43" s="1">
         <v>6.5822784810126587</v>
       </c>
-      <c r="M43">
+      <c r="M43" s="1">
         <v>2.7848101265822778</v>
       </c>
-      <c r="N43">
+      <c r="N43" s="1">
         <v>9.3670886075949369</v>
       </c>
-      <c r="O43">
+      <c r="O43" s="1">
         <v>3.79746835443038</v>
       </c>
-      <c r="P43">
+      <c r="P43" s="1">
         <v>70.270270270270274</v>
       </c>
-      <c r="Q43">
+      <c r="Q43" s="1">
         <v>20</v>
       </c>
-      <c r="R43">
+      <c r="R43" s="1">
         <v>6</v>
       </c>
-      <c r="S43">
+      <c r="S43" s="1">
         <v>20</v>
       </c>
-      <c r="T43">
+      <c r="T43" s="1">
         <v>14</v>
       </c>
-      <c r="U43">
-        <v>0</v>
-      </c>
-      <c r="V43">
+      <c r="U43" s="1">
+        <v>0</v>
+      </c>
+      <c r="V43" s="1">
         <v>14</v>
       </c>
-      <c r="W43">
+      <c r="W43" s="3">
         <v>3.0384615384615379</v>
       </c>
-      <c r="X43">
+      <c r="X43" s="3">
         <v>2.1545454545454552</v>
       </c>
-      <c r="Y43">
+      <c r="Y43" s="3">
         <v>2.1351351351351351</v>
       </c>
-      <c r="Z43" t="s">
+      <c r="Z43" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AA43">
+      <c r="AA43" s="3">
         <v>11.39240506329114</v>
       </c>
-      <c r="AB43" t="s">
+      <c r="AB43" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC43">
+      <c r="AC43" s="3">
         <v>11.39240506329114</v>
       </c>
-      <c r="AD43">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="s">
+      <c r="AD43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG43" t="s">
+      <c r="AG43" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH43">
+      <c r="AH43" s="1">
         <v>1</v>
       </c>
       <c r="AI43" t="s">
@@ -7711,7 +7769,7 @@
       <c r="AN43" t="s">
         <v>133</v>
       </c>
-      <c r="AO43" t="s">
+      <c r="AO43" s="1" t="s">
         <v>415</v>
       </c>
       <c r="AP43" t="s">
@@ -7739,7 +7797,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="44" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>346</v>
       </c>
@@ -7755,82 +7813,82 @@
       <c r="E44" t="s">
         <v>112</v>
       </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44">
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
         <v>4</v>
       </c>
-      <c r="K44">
+      <c r="K44" s="1">
         <v>496</v>
       </c>
-      <c r="L44">
+      <c r="L44" s="1">
         <v>6.4516129032258061</v>
       </c>
-      <c r="M44">
+      <c r="M44" s="1">
         <v>1.008064516129032</v>
       </c>
-      <c r="N44">
+      <c r="N44" s="1">
         <v>7.4596774193548381</v>
       </c>
-      <c r="O44">
+      <c r="O44" s="1">
         <v>5.443548387096774</v>
       </c>
-      <c r="P44">
+      <c r="P44" s="1">
         <v>86.486486486486484</v>
       </c>
-      <c r="Q44">
+      <c r="Q44" s="1">
         <v>20</v>
       </c>
-      <c r="R44">
+      <c r="R44" s="1">
         <v>2</v>
       </c>
-      <c r="S44">
+      <c r="S44" s="1">
         <v>21</v>
       </c>
-      <c r="T44">
+      <c r="T44" s="1">
         <v>18</v>
       </c>
-      <c r="U44">
-        <v>1</v>
-      </c>
-      <c r="V44">
+      <c r="U44" s="1">
+        <v>1</v>
+      </c>
+      <c r="V44" s="1">
         <v>19</v>
       </c>
-      <c r="W44">
+      <c r="W44" s="3">
         <v>3.1</v>
       </c>
-      <c r="X44">
+      <c r="X44" s="3">
         <v>1.984</v>
       </c>
-      <c r="Y44">
+      <c r="Y44" s="3">
         <v>2.8151351351351348</v>
       </c>
-      <c r="Z44" t="s">
+      <c r="Z44" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AA44">
+      <c r="AA44" s="3">
         <v>11.49193548387097</v>
       </c>
-      <c r="AB44" t="s">
+      <c r="AB44" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AC44">
+      <c r="AC44" s="3">
         <v>11.49193548387097</v>
       </c>
-      <c r="AD44">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="s">
+      <c r="AD44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AG44" t="s">
+      <c r="AG44" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AH44">
+      <c r="AH44" s="1">
         <v>2</v>
       </c>
       <c r="AI44" t="s">
@@ -7851,7 +7909,7 @@
       <c r="AN44" t="s">
         <v>133</v>
       </c>
-      <c r="AO44" t="s">
+      <c r="AO44" s="1" t="s">
         <v>263</v>
       </c>
       <c r="AP44" t="s">
@@ -7887,9 +7945,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7906,7 +7964,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>163</v>
       </c>
@@ -7923,7 +7981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -7940,7 +7998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>256</v>
       </c>
@@ -7957,7 +8015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>346</v>
       </c>
@@ -7982,9 +8040,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8001,7 +8059,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>163</v>
       </c>
@@ -8018,7 +8076,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -8035,7 +8093,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>256</v>
       </c>
@@ -8052,7 +8110,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>346</v>
       </c>
@@ -8077,9 +8135,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8096,7 +8154,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>163</v>
       </c>
@@ -8113,7 +8171,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -8130,7 +8188,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>256</v>
       </c>
@@ -8147,7 +8205,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>346</v>
       </c>
@@ -8172,9 +8230,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8191,7 +8249,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>163</v>
       </c>
@@ -8208,7 +8266,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -8225,7 +8283,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>256</v>
       </c>
@@ -8242,7 +8300,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>346</v>
       </c>
